--- a/TMS/其他/combi1ned_data.xlsx
+++ b/TMS/其他/combi1ned_data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="153">
   <si>
     <t>country</t>
   </si>
@@ -104,109 +104,388 @@
     <t>502</t>
   </si>
   <si>
+    <t>A*******A</t>
+  </si>
+  <si>
+    <t>35059</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>TK</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>6404199000</t>
+  </si>
+  <si>
+    <t>1|0|未过踝|鞋面材料:合成革/混纺布/橡塑材料|合成革|安踏|812221601-5</t>
+  </si>
+  <si>
+    <t>鞋</t>
+  </si>
+  <si>
+    <t>112417718-7</t>
+  </si>
+  <si>
+    <t>TN5102200916214</t>
+  </si>
+  <si>
+    <t>MX5102200916214</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>7.37900,0.73934</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>H*******J</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:网布/合成革/橡塑材料|外底材料:EVA|品牌:中文品牌:安踏 英文品牌:ANTA|货号:912415523-3|||</t>
+  </si>
+  <si>
+    <t>休闲鞋</t>
+  </si>
+  <si>
+    <t>912415523-3</t>
+  </si>
+  <si>
+    <t>TN5102100916185</t>
+  </si>
+  <si>
+    <t>MX5102100916185</t>
+  </si>
+  <si>
+    <t>S*******P</t>
+  </si>
+  <si>
+    <t>TN5102100916184</t>
+  </si>
+  <si>
+    <t>MX5102100916184</t>
+  </si>
+  <si>
+    <t>S*******D</t>
+  </si>
+  <si>
+    <t>6117809000</t>
+  </si>
+  <si>
+    <t>1|0|织造方法:针织|成分含量:锦纶94.5%氨纶5.5%|品牌:中文品牌:安踏 英文品牌:ANTA|||</t>
+  </si>
+  <si>
+    <t>头带</t>
+  </si>
+  <si>
+    <t>1824572501-1</t>
+  </si>
+  <si>
+    <t>TN5102100916170</t>
+  </si>
+  <si>
+    <t>MX5102100916170</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>F*******A</t>
+  </si>
+  <si>
+    <t>SHOPEE</t>
+  </si>
+  <si>
+    <t>6402992900</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:合成革/网布|外底材料:EVA/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:122418016-2|||</t>
+  </si>
+  <si>
+    <t>122418016-2</t>
+  </si>
+  <si>
+    <t>TN5102100916165</t>
+  </si>
+  <si>
+    <t>MX5102100916165</t>
+  </si>
+  <si>
     <t>M*******E</t>
   </si>
   <si>
-    <t>35059</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>SHOPEE</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>6404199000</t>
-  </si>
-  <si>
-    <t>1|0|未过踝|鞋面材料:合成革/混纺布/橡塑材料|合成革|安踏|812221601-5</t>
-  </si>
-  <si>
-    <t>鞋</t>
-  </si>
-  <si>
-    <t>112417718-7</t>
-  </si>
-  <si>
     <t>TN5102100916164</t>
   </si>
   <si>
     <t>MX5102100916164</t>
   </si>
   <si>
-    <t>025</t>
-  </si>
-  <si>
-    <t>USD</t>
+    <t>7.37900</t>
+  </si>
+  <si>
+    <t>H*******S</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:网布/TPU|外底材料:TPU/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:122415582-9|||</t>
+  </si>
+  <si>
+    <t>122415582-9</t>
+  </si>
+  <si>
+    <t>TN5102100916163</t>
+  </si>
+  <si>
+    <t>MX5102100916163</t>
+  </si>
+  <si>
+    <t>F*******E</t>
+  </si>
+  <si>
+    <t>LAZA</t>
+  </si>
+  <si>
+    <t>TN5102100916161</t>
+  </si>
+  <si>
+    <t>MX5102100916161</t>
+  </si>
+  <si>
+    <t>5.96700</t>
+  </si>
+  <si>
+    <t>J*******L</t>
+  </si>
+  <si>
+    <t>TN5102100916159</t>
+  </si>
+  <si>
+    <t>MX5102100916159</t>
+  </si>
+  <si>
+    <t>8.77500</t>
+  </si>
+  <si>
+    <t>G*******K</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:网布/橡塑材料|外底材料:TPU/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:112445581-5|||</t>
+  </si>
+  <si>
+    <t>112445581-5</t>
+  </si>
+  <si>
+    <t>TN5102000916126</t>
+  </si>
+  <si>
+    <t>MX5102000916126</t>
+  </si>
+  <si>
+    <t>12.28500</t>
+  </si>
+  <si>
+    <t>I*******P</t>
+  </si>
+  <si>
+    <t>TN5102000916113</t>
+  </si>
+  <si>
+    <t>MX5102000916113</t>
+  </si>
+  <si>
+    <t>17.55000</t>
+  </si>
+  <si>
+    <t>D*******Z</t>
+  </si>
+  <si>
+    <t>TN5102000916070</t>
+  </si>
+  <si>
+    <t>MX5102000916070</t>
+  </si>
+  <si>
+    <t>2.50886</t>
+  </si>
+  <si>
+    <t>I*******C</t>
+  </si>
+  <si>
+    <t>1|0|织造方法:针织|成分含量:锦纶88%氨纶12%|品牌:中文品牌:安踏 英文品牌:ANTA|||</t>
+  </si>
+  <si>
+    <t>护膝</t>
+  </si>
+  <si>
+    <t>1824472577-1</t>
+  </si>
+  <si>
+    <t>TN5102000916056</t>
+  </si>
+  <si>
+    <t>MX5102000916056</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>7.82174</t>
+  </si>
+  <si>
+    <t>N*******T</t>
+  </si>
+  <si>
+    <t>TN5102000916032</t>
+  </si>
+  <si>
+    <t>MX5102000916032</t>
+  </si>
+  <si>
+    <t>U*******S</t>
+  </si>
+  <si>
+    <t>TN5102000916030</t>
+  </si>
+  <si>
+    <t>MX5102000916030</t>
+  </si>
+  <si>
+    <t>0.88548</t>
+  </si>
+  <si>
+    <t>C*******F</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:网布/橡塑材料|外底材料:TPU/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:112415582-9|||</t>
+  </si>
+  <si>
+    <t>112415582-9</t>
+  </si>
+  <si>
+    <t>TN5102000916022</t>
+  </si>
+  <si>
+    <t>MX5102000916022</t>
+  </si>
+  <si>
+    <t>4.30934</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:网布/橡塑材料|外底材料:TPU/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:112415582-6|||</t>
+  </si>
+  <si>
+    <t>112415582-6</t>
+  </si>
+  <si>
+    <t>X*******T</t>
+  </si>
+  <si>
+    <t>TN5102000915709</t>
+  </si>
+  <si>
+    <t>MX5102000915709</t>
+  </si>
+  <si>
+    <t>12.98704</t>
+  </si>
+  <si>
+    <t>1|0|款式:未过踝|鞋面材料:合成革/网布|外底材料:EVA/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:122418016-3|||</t>
+  </si>
+  <si>
+    <t>122418016-3</t>
   </si>
   <si>
     <t>J*******F</t>
   </si>
   <si>
-    <t>1|0|款式:未过踝|鞋面材料:网布/橡塑材料|外底材料:TPU/橡胶|品牌:中文品牌:安踏 英文品牌:ANTA|货号:112445581-5|||</t>
-  </si>
-  <si>
-    <t>休闲鞋</t>
-  </si>
-  <si>
-    <t>112445581-5</t>
-  </si>
-  <si>
     <t>TN5102000915680</t>
   </si>
   <si>
     <t>MX5102000915680</t>
   </si>
   <si>
-    <t>G*******K</t>
-  </si>
-  <si>
-    <t>LAZA</t>
-  </si>
-  <si>
-    <t>TN5102000916126</t>
-  </si>
-  <si>
-    <t>MX5102000916126</t>
-  </si>
-  <si>
-    <t>U*******S</t>
-  </si>
-  <si>
-    <t>TK</t>
-  </si>
-  <si>
-    <t>6117809000</t>
-  </si>
-  <si>
-    <t>1|0|织造方法:针织|成分含量:锦纶88%氨纶12%|品牌:中文品牌:安踏 英文品牌:ANTA|||</t>
-  </si>
-  <si>
-    <t>护膝</t>
-  </si>
-  <si>
-    <t>1824472577-1</t>
-  </si>
-  <si>
-    <t>TN5102000916030</t>
-  </si>
-  <si>
-    <t>MX5102000916030</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
-    <t>N*******T</t>
-  </si>
-  <si>
-    <t>TN5102000916032</t>
-  </si>
-  <si>
-    <t>MX5102000916032</t>
+    <t>4.72256</t>
+  </si>
+  <si>
+    <t>V*******G</t>
+  </si>
+  <si>
+    <t>6109909000</t>
+  </si>
+  <si>
+    <t>1|0|织造方法:针织|类别:女式|是否有领:无领|是否有扣:无扣|是否有拉链:无拉链|成分含量:聚酯纤维100%|品牌:中文品牌:安踏 英文品牌:ANTA|货号:962427101-7|||</t>
+  </si>
+  <si>
+    <t>女式T恤</t>
+  </si>
+  <si>
+    <t>962427101-7</t>
+  </si>
+  <si>
+    <t>TN_580621142107719026</t>
+  </si>
+  <si>
+    <t>CWB_580621142107719026</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>8.85480</t>
+  </si>
+  <si>
+    <t>1|0|织造方法:针织|类别:女式|是否有领:无领|是否有扣:无扣|是否有拉链:无拉链|成分含量:聚酯纤维92%氨纶8%|品牌:中文品牌:安踏 英文品牌:ANTA|货号:162537101U-1|||</t>
+  </si>
+  <si>
+    <t>962427101-2</t>
+  </si>
+  <si>
+    <t>V*******Y</t>
+  </si>
+  <si>
+    <t>PH234478390772D</t>
+  </si>
+  <si>
+    <t>CWB_580710983291275195</t>
+  </si>
+  <si>
+    <t>5.84417</t>
+  </si>
+  <si>
+    <t>O*******M</t>
+  </si>
+  <si>
+    <t>LXBPH000263888889</t>
+  </si>
+  <si>
+    <t>MX5102400916261</t>
+  </si>
+  <si>
+    <t>12.10156</t>
+  </si>
+  <si>
+    <t>I*******U</t>
+  </si>
+  <si>
+    <t>LXBPH000263888888</t>
+  </si>
+  <si>
+    <t>MX5102400916260</t>
+  </si>
+  <si>
+    <t>X*******Q</t>
+  </si>
+  <si>
+    <t>LXBMY000107073760</t>
+  </si>
+  <si>
+    <t>CWB_580598436764026792</t>
   </si>
 </sst>
 </file>
@@ -849,10 +1128,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1210,83 +1493,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:W35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="18" max="18" width="22.1818181818182" customWidth="1"/>
-    <col min="21" max="21" width="16.2727272727273" customWidth="1"/>
-    <col min="22" max="22" width="26.3636363636364" customWidth="1"/>
+    <col min="18" max="18" width="25.2727272727273" customWidth="1"/>
+    <col min="20" max="20" width="9" style="1"/>
     <col min="23" max="23" width="24.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1334,7 +1616,7 @@
         <v>0.7</v>
       </c>
       <c r="O2">
-        <v>40.02</v>
+        <v>6.26</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -1348,17 +1630,14 @@
       <c r="S2" t="s">
         <v>36</v>
       </c>
-      <c r="T2">
-        <v>7.379</v>
-      </c>
-      <c r="U2">
-        <v>7.28031</v>
+      <c r="T2" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1369,7 +1648,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -1387,49 +1666,43 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3">
         <v>0.001</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="O3">
-        <v>107.14</v>
+        <v>0.01</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>
       </c>
-      <c r="T3">
-        <v>4.72256</v>
-      </c>
-      <c r="U3">
-        <v>19.48933</v>
-      </c>
       <c r="V3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -1440,7 +1713,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1449,7 +1722,7 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1458,31 +1731,31 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>0.001</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
         <v>46</v>
       </c>
       <c r="N4">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="O4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="R4" t="s">
         <v>47</v>
@@ -1490,17 +1763,11 @@
       <c r="S4" t="s">
         <v>36</v>
       </c>
-      <c r="T4">
-        <v>12.285</v>
-      </c>
-      <c r="U4">
-        <v>0.00807</v>
-      </c>
       <c r="V4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1511,7 +1778,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -1520,58 +1787,58 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>0.001</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="N5">
-        <v>0.81</v>
+        <v>0.02</v>
       </c>
       <c r="O5">
-        <v>0.02</v>
+        <v>10.77</v>
       </c>
       <c r="P5">
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>0.81</v>
+        <v>0.02</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5">
-        <v>12.285</v>
+        <v>55</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1.62338</v>
       </c>
       <c r="U5">
-        <v>0.00807</v>
+        <v>2.53604</v>
       </c>
       <c r="V5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1591,58 +1858,58 @@
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
         <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
       </c>
       <c r="J6">
         <v>0.001</v>
       </c>
       <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s">
         <v>52</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>53</v>
       </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
       <c r="N6">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
       <c r="O6">
-        <v>8742.67</v>
+        <v>10.77</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
       <c r="R6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" t="s">
         <v>55</v>
       </c>
-      <c r="S6" t="s">
-        <v>56</v>
-      </c>
-      <c r="T6">
-        <v>0.88548</v>
+      <c r="T6" s="1">
+        <v>1.62338</v>
       </c>
       <c r="U6">
-        <v>2058.02422</v>
+        <v>2.53604</v>
       </c>
       <c r="V6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1653,7 +1920,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1662,58 +1929,58 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J7">
         <v>0.001</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N7">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="O7">
-        <v>8742.67</v>
+        <v>26.42</v>
       </c>
       <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="S7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T7">
-        <v>0.88548</v>
+        <v>36</v>
+      </c>
+      <c r="T7" s="1">
+        <v>5.01772</v>
       </c>
       <c r="U7">
-        <v>2058.02422</v>
+        <v>4.80522</v>
       </c>
       <c r="V7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1724,7 +1991,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -1733,7 +2000,7 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -1754,13 +2021,13 @@
         <v>33</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="N8">
         <v>0.7</v>
       </c>
       <c r="O8">
-        <v>6.26</v>
+        <v>40.02</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1769,22 +2036,1939 @@
         <v>0.7</v>
       </c>
       <c r="R8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="S8" t="s">
         <v>36</v>
       </c>
-      <c r="T8">
-        <v>7.379</v>
+      <c r="T8" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="U8">
+        <v>7.28031</v>
+      </c>
+      <c r="V8" t="s">
+        <v>38</v>
+      </c>
+      <c r="W8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9">
+        <v>0.001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9">
+        <v>0.74</v>
+      </c>
+      <c r="O9">
+        <v>40.02</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0.74</v>
+      </c>
+      <c r="R9" t="s">
+        <v>71</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="U9">
+        <v>7.28031</v>
+      </c>
+      <c r="V9" t="s">
+        <v>38</v>
+      </c>
+      <c r="W9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10">
+        <v>0.001</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N10">
+        <v>0.7</v>
+      </c>
+      <c r="O10">
+        <v>0.08</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0.7</v>
+      </c>
+      <c r="R10" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="U10">
+        <v>0.01601</v>
+      </c>
+      <c r="V10" t="s">
+        <v>38</v>
+      </c>
+      <c r="W10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11">
+        <v>0.001</v>
+      </c>
+      <c r="K11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" t="s">
+        <v>78</v>
+      </c>
+      <c r="N11">
+        <v>0.74</v>
+      </c>
+      <c r="O11">
+        <v>0.03</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0.74</v>
+      </c>
+      <c r="R11" t="s">
+        <v>79</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="U11">
+        <v>0.00585</v>
+      </c>
+      <c r="V11" t="s">
+        <v>38</v>
+      </c>
+      <c r="W11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12">
+        <v>0.001</v>
+      </c>
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12">
+        <v>0.81</v>
+      </c>
+      <c r="O12">
+        <v>0.02</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0.81</v>
+      </c>
+      <c r="R12" t="s">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U12">
+        <v>0.00807</v>
+      </c>
+      <c r="V12" t="s">
+        <v>38</v>
+      </c>
+      <c r="W12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13">
+        <v>0.001</v>
+      </c>
+      <c r="K13" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" t="s">
+        <v>84</v>
+      </c>
+      <c r="N13">
+        <v>0.81</v>
+      </c>
+      <c r="O13">
+        <v>0.02</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0.81</v>
+      </c>
+      <c r="R13" t="s">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U13">
+        <v>0.00807</v>
+      </c>
+      <c r="V13" t="s">
+        <v>38</v>
+      </c>
+      <c r="W13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14">
+        <v>0.001</v>
+      </c>
+      <c r="K14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" t="s">
+        <v>88</v>
+      </c>
+      <c r="N14">
+        <v>0.74</v>
+      </c>
+      <c r="O14">
+        <v>0.01</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0.74</v>
+      </c>
+      <c r="R14" t="s">
+        <v>89</v>
+      </c>
+      <c r="S14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U14">
+        <v>0.00292</v>
+      </c>
+      <c r="V14" t="s">
+        <v>38</v>
+      </c>
+      <c r="W14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15">
+        <v>0.001</v>
+      </c>
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15">
+        <v>0.74</v>
+      </c>
+      <c r="O15">
+        <v>0.01</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0.74</v>
+      </c>
+      <c r="R15" t="s">
+        <v>89</v>
+      </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U15">
+        <v>0.00292</v>
+      </c>
+      <c r="V15" t="s">
+        <v>38</v>
+      </c>
+      <c r="W15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16">
+        <v>0.001</v>
+      </c>
+      <c r="K16" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" t="s">
+        <v>92</v>
+      </c>
+      <c r="N16">
+        <v>0.87</v>
+      </c>
+      <c r="O16">
+        <v>61.88</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0.87</v>
+      </c>
+      <c r="R16" t="s">
+        <v>93</v>
+      </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U16">
+        <v>7.28331</v>
+      </c>
+      <c r="V16" t="s">
+        <v>38</v>
+      </c>
+      <c r="W16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17">
+        <v>0.001</v>
+      </c>
+      <c r="K17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17" t="s">
+        <v>99</v>
+      </c>
+      <c r="N17">
+        <v>0.15</v>
+      </c>
+      <c r="O17">
+        <v>24.94</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0.15</v>
+      </c>
+      <c r="R17" t="s">
+        <v>100</v>
+      </c>
+      <c r="S17" t="s">
+        <v>101</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="U17">
+        <v>7.35105</v>
+      </c>
+      <c r="V17" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18">
+        <v>0.001</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" t="s">
+        <v>99</v>
+      </c>
+      <c r="N18">
+        <v>0.7</v>
+      </c>
+      <c r="O18">
+        <v>37.51</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0.7</v>
+      </c>
+      <c r="R18" t="s">
+        <v>100</v>
+      </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="U18">
+        <v>7.35105</v>
+      </c>
+      <c r="V18" t="s">
+        <v>38</v>
+      </c>
+      <c r="W18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19">
+        <v>0.001</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19" t="s">
+        <v>104</v>
+      </c>
+      <c r="N19">
+        <v>0.7</v>
+      </c>
+      <c r="O19">
+        <v>6.26</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0.7</v>
+      </c>
+      <c r="R19" t="s">
+        <v>105</v>
+      </c>
+      <c r="S19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="U19">
         <v>0.73934</v>
       </c>
-      <c r="V8" t="s">
-        <v>37</v>
-      </c>
-      <c r="W8" t="s">
-        <v>37</v>
+      <c r="V19" t="s">
+        <v>38</v>
+      </c>
+      <c r="W19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20">
+        <v>0.001</v>
+      </c>
+      <c r="K20" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+      <c r="M20" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20">
+        <v>0.15</v>
+      </c>
+      <c r="O20">
+        <v>8742.67</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0.15</v>
+      </c>
+      <c r="R20" t="s">
+        <v>108</v>
+      </c>
+      <c r="S20" t="s">
+        <v>101</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U20">
+        <v>2058.02422</v>
+      </c>
+      <c r="V20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21">
+        <v>0.001</v>
+      </c>
+      <c r="K21" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" t="s">
+        <v>98</v>
+      </c>
+      <c r="M21" t="s">
+        <v>107</v>
+      </c>
+      <c r="N21">
+        <v>0.15</v>
+      </c>
+      <c r="O21">
+        <v>8742.67</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0.15</v>
+      </c>
+      <c r="R21" t="s">
+        <v>108</v>
+      </c>
+      <c r="S21" t="s">
+        <v>101</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U21">
+        <v>2058.02422</v>
+      </c>
+      <c r="V21" t="s">
+        <v>38</v>
+      </c>
+      <c r="W21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22">
+        <v>0.001</v>
+      </c>
+      <c r="K22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M22" t="s">
+        <v>113</v>
+      </c>
+      <c r="N22">
+        <v>0.9</v>
+      </c>
+      <c r="O22">
+        <v>7.43</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0.9</v>
+      </c>
+      <c r="R22" t="s">
+        <v>114</v>
+      </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U22">
+        <v>1.74918</v>
+      </c>
+      <c r="V22" t="s">
+        <v>38</v>
+      </c>
+      <c r="W22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>116</v>
+      </c>
+      <c r="J23">
+        <v>0.001</v>
+      </c>
+      <c r="K23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" t="s">
+        <v>117</v>
+      </c>
+      <c r="M23" t="s">
+        <v>113</v>
+      </c>
+      <c r="N23">
+        <v>0.87</v>
+      </c>
+      <c r="O23">
+        <v>7.43</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0.87</v>
+      </c>
+      <c r="R23" t="s">
+        <v>114</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U23">
+        <v>1.74918</v>
+      </c>
+      <c r="V23" t="s">
+        <v>38</v>
+      </c>
+      <c r="W23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24">
+        <v>0.001</v>
+      </c>
+      <c r="K24" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" t="s">
+        <v>119</v>
+      </c>
+      <c r="N24">
+        <v>0.7</v>
+      </c>
+      <c r="O24">
+        <v>37.66</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0.7</v>
+      </c>
+      <c r="R24" t="s">
+        <v>120</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U24">
+        <v>13.70159</v>
+      </c>
+      <c r="V24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25">
+        <v>0.001</v>
+      </c>
+      <c r="K25" t="s">
+        <v>41</v>
+      </c>
+      <c r="L25" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25" t="s">
+        <v>119</v>
+      </c>
+      <c r="N25">
+        <v>0.7</v>
+      </c>
+      <c r="O25">
+        <v>37.66</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0.7</v>
+      </c>
+      <c r="R25" t="s">
+        <v>120</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U25">
+        <v>13.70159</v>
+      </c>
+      <c r="V25" t="s">
+        <v>38</v>
+      </c>
+      <c r="W25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26">
+        <v>0.001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" t="s">
+        <v>125</v>
+      </c>
+      <c r="N26">
+        <v>0.81</v>
+      </c>
+      <c r="O26">
+        <v>107.14</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>0.81</v>
+      </c>
+      <c r="R26" t="s">
+        <v>126</v>
+      </c>
+      <c r="S26" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="U26">
+        <v>19.48933</v>
+      </c>
+      <c r="V26" t="s">
+        <v>38</v>
+      </c>
+      <c r="W26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" t="s">
+        <v>130</v>
+      </c>
+      <c r="J27">
+        <v>0.001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" t="s">
+        <v>132</v>
+      </c>
+      <c r="M27" t="s">
+        <v>133</v>
+      </c>
+      <c r="N27">
+        <v>0.1</v>
+      </c>
+      <c r="O27">
+        <v>16.41</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" t="s">
+        <v>134</v>
+      </c>
+      <c r="S27" t="s">
+        <v>135</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="U27">
+        <v>3.86312</v>
+      </c>
+      <c r="V27" t="s">
+        <v>38</v>
+      </c>
+      <c r="W27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28">
+        <v>0.001</v>
+      </c>
+      <c r="K28" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28" t="s">
+        <v>138</v>
+      </c>
+      <c r="M28" t="s">
+        <v>133</v>
+      </c>
+      <c r="N28">
+        <v>0.1</v>
+      </c>
+      <c r="O28">
+        <v>16.41</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28" t="s">
+        <v>134</v>
+      </c>
+      <c r="S28" t="s">
+        <v>135</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="U28">
+        <v>3.86312</v>
+      </c>
+      <c r="V28" t="s">
+        <v>38</v>
+      </c>
+      <c r="W28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29">
+        <v>0.001</v>
+      </c>
+      <c r="K29" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" t="s">
+        <v>140</v>
+      </c>
+      <c r="N29">
+        <v>0.87</v>
+      </c>
+      <c r="O29">
+        <v>22558.99</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>0.87</v>
+      </c>
+      <c r="R29" t="s">
+        <v>141</v>
+      </c>
+      <c r="S29" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U29">
+        <v>7633.26386</v>
+      </c>
+      <c r="V29" t="s">
+        <v>38</v>
+      </c>
+      <c r="W29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" t="s">
+        <v>50</v>
+      </c>
+      <c r="J30">
+        <v>0.001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>51</v>
+      </c>
+      <c r="L30" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" t="s">
+        <v>140</v>
+      </c>
+      <c r="N30">
+        <v>0.02</v>
+      </c>
+      <c r="O30">
+        <v>19735.58</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <v>0.02</v>
+      </c>
+      <c r="R30" t="s">
+        <v>141</v>
+      </c>
+      <c r="S30" t="s">
+        <v>55</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U30">
+        <v>7633.26386</v>
+      </c>
+      <c r="V30" t="s">
+        <v>38</v>
+      </c>
+      <c r="W30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31">
+        <v>0.001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>33</v>
+      </c>
+      <c r="M31" t="s">
+        <v>144</v>
+      </c>
+      <c r="N31">
+        <v>0.7</v>
+      </c>
+      <c r="O31">
+        <v>52.98</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>0.7</v>
+      </c>
+      <c r="R31" t="s">
+        <v>145</v>
+      </c>
+      <c r="S31" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U31">
+        <v>28.40717</v>
+      </c>
+      <c r="V31" t="s">
+        <v>38</v>
+      </c>
+      <c r="W31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" t="s">
+        <v>82</v>
+      </c>
+      <c r="J32">
+        <v>0.001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" t="s">
+        <v>83</v>
+      </c>
+      <c r="M32" t="s">
+        <v>144</v>
+      </c>
+      <c r="N32">
+        <v>0.81</v>
+      </c>
+      <c r="O32">
+        <v>103.19</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>0.81</v>
+      </c>
+      <c r="R32" t="s">
+        <v>145</v>
+      </c>
+      <c r="S32" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U32">
+        <v>28.40717</v>
+      </c>
+      <c r="V32" t="s">
+        <v>38</v>
+      </c>
+      <c r="W32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33">
+        <v>0.001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33" t="s">
+        <v>148</v>
+      </c>
+      <c r="N33">
+        <v>0.7</v>
+      </c>
+      <c r="O33">
+        <v>0.19</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <v>0.7</v>
+      </c>
+      <c r="R33" t="s">
+        <v>149</v>
+      </c>
+      <c r="S33" t="s">
+        <v>36</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="U33">
+        <v>0.03642</v>
+      </c>
+      <c r="V33" t="s">
+        <v>38</v>
+      </c>
+      <c r="W33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34">
+        <v>0.001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>41</v>
+      </c>
+      <c r="L34" t="s">
+        <v>83</v>
+      </c>
+      <c r="M34" t="s">
+        <v>151</v>
+      </c>
+      <c r="N34">
+        <v>0.81</v>
+      </c>
+      <c r="O34">
+        <v>7.82</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <v>0.81</v>
+      </c>
+      <c r="R34" t="s">
+        <v>152</v>
+      </c>
+      <c r="S34" t="s">
+        <v>36</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U34">
+        <v>1.84124</v>
+      </c>
+      <c r="V34" t="s">
+        <v>38</v>
+      </c>
+      <c r="W34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35">
+        <v>0.001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" t="s">
+        <v>151</v>
+      </c>
+      <c r="N35">
+        <v>0.7</v>
+      </c>
+      <c r="O35">
+        <v>7.82</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>0.7</v>
+      </c>
+      <c r="R35" t="s">
+        <v>152</v>
+      </c>
+      <c r="S35" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U35">
+        <v>1.84124</v>
+      </c>
+      <c r="V35" t="s">
+        <v>38</v>
+      </c>
+      <c r="W35" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
